--- a/data_store/uploads/Seguimiento hallazgos - Solman.xlsx
+++ b/data_store/uploads/Seguimiento hallazgos - Solman.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JuanEstebanGarciaGal\Documents\IBM\Pipelina-excel-flujo\datos_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{996D974D-51B6-4AC7-852C-CF7844529F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6741FC84-801A-4F99-8558-DF761DA975E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
     <sheet name="informacion_extra" sheetId="2" r:id="rId2"/>
     <sheet name="dinamico" sheetId="3" r:id="rId3"/>
-    <sheet name="seguimiento_defectos" sheetId="1" r:id="rId4"/>
-    <sheet name="Historico " sheetId="4" r:id="rId5"/>
+    <sheet name="seguimiento_detalles_defecto" sheetId="1" r:id="rId4"/>
+    <sheet name="resumen_diario_estado_defectos" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">informacion_extra!$A$1:$F$71</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">seguimiento_defectos!$A$1:$CP$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">seguimiento_detalles_defecto!$A$1:$CP$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
@@ -1967,7 +1967,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Excel Services" refreshedDate="45866.540734837959" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="75" xr:uid="{4CBC1207-BA8F-4219-B24B-54A986911635}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:L69" sheet="seguimiento_defectos"/>
+    <worksheetSource ref="A1:L69" sheet="seguimiento_detalles_defecto"/>
   </cacheSource>
   <cacheFields count="12">
     <cacheField name="N°" numFmtId="0">
@@ -2231,7 +2231,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Excel Services" refreshedDate="45867.378122916663" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="139" xr:uid="{233D30EA-A301-4ACE-BE5D-F2C118C0CE2F}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:L1048576" sheet="seguimiento_defectos"/>
+    <worksheetSource ref="A1:L1048576" sheet="seguimiento_detalles_defecto"/>
   </cacheSource>
   <cacheFields count="12">
     <cacheField name="N°" numFmtId="0">
@@ -2319,7 +2319,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Excel Services" refreshedDate="45867.382960300929" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="139" xr:uid="{E279F014-6D4E-46F7-B6BD-85CC7B95088A}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:M1048576" sheet="seguimiento_defectos"/>
+    <worksheetSource ref="A1:M1048576" sheet="seguimiento_detalles_defecto"/>
   </cacheSource>
   <cacheFields count="13">
     <cacheField name="N°" numFmtId="0">
@@ -2399,7 +2399,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Excel Services" refreshedDate="45867.442092939818" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="71" xr:uid="{21D9BDF5-64AA-4C46-A58D-DC9141F3373C}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:J1048576" sheet="seguimiento_defectos"/>
+    <worksheetSource ref="A1:J1048576" sheet="seguimiento_detalles_defecto"/>
   </cacheSource>
   <cacheFields count="10">
     <cacheField name="N°" numFmtId="0">
@@ -8885,195 +8885,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6A511195-6EFA-4CB5-B296-85E219F2EA15}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A17:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="12">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisCol" dataField="1" compact="0" outline="0" showAll="0">
-      <items count="21">
-        <item m="1" x="19"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item m="1" x="17"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="12"/>
-        <item x="15"/>
-        <item m="1" x="16"/>
-        <item x="13"/>
-        <item m="1" x="18"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="8">
-        <item x="2"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item x="3"/>
-        <item h="1" m="1" x="6"/>
-        <item h="1" x="4"/>
-        <item h="1" m="1" x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
-      <items count="8">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="11">
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="11" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Count of Modulo " fld="2" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="11">
-    <format dxfId="11">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="10">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="9">
-      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="8">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="7">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="6">
-      <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="5">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="8" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="4">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="12">
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="8"/>
-            <x v="9"/>
-            <x v="11"/>
-            <x v="12"/>
-            <x v="13"/>
-            <x v="14"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="2">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="1">
-      <pivotArea grandRow="1" grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C9E40919-F980-4DDB-A407-68DEB46B8375}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A6:O10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="10">
@@ -9224,35 +9035,35 @@
     <dataField name="Count of Modulo " fld="2" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="11">
-    <format dxfId="22">
+    <format dxfId="11">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="10">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="9">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="8">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="7">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="6">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="8" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="4">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="12">
@@ -9272,10 +9083,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="1">
       <pivotArea grandRow="1" grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -9291,7 +9102,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EE1E995E-E053-47CA-B246-0A59CC20181F}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A27:J31" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="13">
@@ -9397,6 +9208,194 @@
     <dataField name="Count of Modulo " fld="2" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="11">
+    <format dxfId="22">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="19">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="2">
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="15">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="8">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="11"/>
+            <x v="14"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea grandRow="1" grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6A511195-6EFA-4CB5-B296-85E219F2EA15}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A17:L21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="12">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" compact="0" outline="0" showAll="0">
+      <items count="21">
+        <item m="1" x="19"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item m="1" x="17"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="12"/>
+        <item x="15"/>
+        <item m="1" x="16"/>
+        <item x="13"/>
+        <item m="1" x="18"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item x="3"/>
+        <item h="1" m="1" x="6"/>
+        <item h="1" x="4"/>
+        <item h="1" m="1" x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+      <items count="8">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="11">
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="11" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of Modulo " fld="2" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="11">
     <format dxfId="33">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
@@ -9418,10 +9417,7 @@
     <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="8" count="2">
-            <x v="1"/>
-            <x v="2"/>
-          </reference>
+          <reference field="8" count="0"/>
         </references>
       </pivotArea>
     </format>
@@ -9431,14 +9427,18 @@
     <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="2" count="8">
-            <x v="0"/>
+          <reference field="2" count="12">
             <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
             <x v="6"/>
-            <x v="7"/>
             <x v="8"/>
             <x v="9"/>
             <x v="11"/>
+            <x v="12"/>
+            <x v="13"/>
             <x v="14"/>
           </reference>
         </references>
@@ -12315,7 +12315,7 @@
         <v>Wilmar Vargas Preciado (174)</v>
       </c>
       <c r="F2" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B2,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B2,informacion_extra!A:F,3,FALSE)</f>
         <v>MONICA PATRICIA GIRALDO PEREZ (192)</v>
       </c>
       <c r="G2" s="39" t="str">
@@ -12359,7 +12359,7 @@
         <v>Alberto Rivera Betancourt (822)</v>
       </c>
       <c r="F3" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B3,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B3,informacion_extra!A:F,3,FALSE)</f>
         <v>SINDY CRISTINA ALZATE ARIAS (201)</v>
       </c>
       <c r="G3" s="39" t="str">
@@ -12401,7 +12401,7 @@
         <v>Nurky Castro (46)</v>
       </c>
       <c r="F4" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B4,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B4,informacion_extra!A:F,3,FALSE)</f>
         <v>ANGELA PATRICIA PERDOMO (175)</v>
       </c>
       <c r="G4" s="39" t="str">
@@ -12440,7 +12440,7 @@
         <v>Pedro Emilio Jimenez Pabon (139)</v>
       </c>
       <c r="F5" s="22" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B5,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B5,informacion_extra!A:F,3,FALSE)</f>
         <v>NATALIA EUGENIA RAMIREZ MOLINA (193)</v>
       </c>
       <c r="G5" s="30" t="str">
@@ -12482,7 +12482,7 @@
         <v>NATALIA EUGENIA RAMIREZ MOLINA (193)</v>
       </c>
       <c r="F6" s="26" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B6,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B6,informacion_extra!A:F,3,FALSE)</f>
         <v>NATALIA EUGENIA RAMIREZ MOLINA (193)</v>
       </c>
       <c r="G6" s="45" t="str">
@@ -12523,7 +12523,7 @@
         <v>Natalia Manzaneda Palacios (258)</v>
       </c>
       <c r="F7" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B7,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B7,informacion_extra!A:F,3,FALSE)</f>
         <v>ANA MILENA IBARBO GUTIERREZ (320)</v>
       </c>
       <c r="G7" s="39" t="str">
@@ -12563,7 +12563,7 @@
         <v>PAOLA ANDREA JIMENEZ RODRIGUEZ (492)</v>
       </c>
       <c r="F8" s="26" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B8,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B8,informacion_extra!A:F,3,FALSE)</f>
         <v>PAOLA ANDREA JIMENEZ RODRIGUEZ (492)</v>
       </c>
       <c r="G8" s="45" t="str">
@@ -12604,7 +12604,7 @@
         <v>Wilmar Vargas Preciado (174)</v>
       </c>
       <c r="F9" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B9,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B9,informacion_extra!A:F,3,FALSE)</f>
         <v>SINDY CRISTINA ALZATE ARIAS (201)</v>
       </c>
       <c r="G9" s="39" t="str">
@@ -12648,7 +12648,7 @@
         <v>MANUEL HERNANDO SANTA JARA (132)</v>
       </c>
       <c r="F10" s="22" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B10,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B10,informacion_extra!A:F,3,FALSE)</f>
         <v>MANUEL HERNANDO SANTA JARA (132)</v>
       </c>
       <c r="G10" s="30" t="str">
@@ -12690,7 +12690,7 @@
         <v>GUSTAVO ADOLFO GARCIA TRUJILLO (393)</v>
       </c>
       <c r="F11" s="26" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B11,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B11,informacion_extra!A:F,3,FALSE)</f>
         <v>GUSTAVO ADOLFO GARCIA TRUJILLO (393)</v>
       </c>
       <c r="G11" s="45" t="str">
@@ -12730,7 +12730,7 @@
         <v>Nicolas Sarmiento (218)</v>
       </c>
       <c r="F12" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B12,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B12,informacion_extra!A:F,3,FALSE)</f>
         <v>DAMARIS BIVIANA MURCIA SABOYA (103)</v>
       </c>
       <c r="G12" s="39" t="str">
@@ -12774,7 +12774,7 @@
         <v>Raphael Gustavo Gimenes Trivaleti (219)</v>
       </c>
       <c r="F13" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B13,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B13,informacion_extra!A:F,3,FALSE)</f>
         <v>JUAN DAVID VARGAS RESTREPO (127)</v>
       </c>
       <c r="G13" s="62" t="str">
@@ -12896,7 +12896,7 @@
         <v>GUSTAVO ESPINOSA (646)</v>
       </c>
       <c r="F14" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B14,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B14,informacion_extra!A:F,3,FALSE)</f>
         <v>LUIS GERMAN PINEDA ARCILA (191)</v>
       </c>
       <c r="G14" s="39" t="str">
@@ -13020,7 +13020,7 @@
         <v>CAROLINA ECHEVERRI SANTA (783)</v>
       </c>
       <c r="F15" s="52" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B15,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B15,informacion_extra!A:F,3,FALSE)</f>
         <v>CAROLINA ECHEVERRI SANTA (783)</v>
       </c>
       <c r="G15" s="36" t="str">
@@ -13062,7 +13062,7 @@
         <v>SANDRA JANET TAMAYO BEDOYA (199)</v>
       </c>
       <c r="F16" s="49" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B16,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B16,informacion_extra!A:F,3,FALSE)</f>
         <v>SANDRA JANET TAMAYO BEDOYA (199)</v>
       </c>
       <c r="G16" s="50" t="str">
@@ -13105,7 +13105,7 @@
         <v>John Alejandro Rodriguez (41)</v>
       </c>
       <c r="F17" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B17,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B17,informacion_extra!A:F,3,FALSE)</f>
         <v>GLORIA ELENA AGUDELO ARENAS (181)</v>
       </c>
       <c r="G17" s="39" t="str">
@@ -13152,7 +13152,7 @@
         <v>NATALIA EUGENIA RAMIREZ MOLINA (193)</v>
       </c>
       <c r="F18" s="52" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B18,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B18,informacion_extra!A:F,3,FALSE)</f>
         <v>NATALIA EUGENIA RAMIREZ MOLINA (193)</v>
       </c>
       <c r="G18" s="36" t="str">
@@ -13195,7 +13195,7 @@
         <v>ANA MILENA CHADID JARAMILLO (697)</v>
       </c>
       <c r="F19" s="22" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B19,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B19,informacion_extra!A:F,3,FALSE)</f>
         <v>ANA MILENA CHADID JARAMILLO (697)</v>
       </c>
       <c r="G19" s="30" t="str">
@@ -13238,7 +13238,7 @@
         <v>ANA MILENA CHADID JARAMILLO (697)</v>
       </c>
       <c r="F20" s="22" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B20,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B20,informacion_extra!A:F,3,FALSE)</f>
         <v>ANA MILENA CHADID JARAMILLO (697)</v>
       </c>
       <c r="G20" s="30" t="str">
@@ -13279,7 +13279,7 @@
         <v>GUSTAVO ESPINOSA (646)</v>
       </c>
       <c r="F21" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B21,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B21,informacion_extra!A:F,3,FALSE)</f>
         <v>PAOLA ANDREA JIMENEZ RODRIGUEZ (492)</v>
       </c>
       <c r="G21" s="39" t="str">
@@ -13324,7 +13324,7 @@
         <v>Nicolas Sarmiento (218)</v>
       </c>
       <c r="F22" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B22,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B22,informacion_extra!A:F,3,FALSE)</f>
         <v>DAMARIS BIVIANA MURCIA SABOYA (103)</v>
       </c>
       <c r="G22" s="39" t="str">
@@ -13450,7 +13450,7 @@
         <v>Nicolas Sarmiento (218)</v>
       </c>
       <c r="F23" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B23,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B23,informacion_extra!A:F,3,FALSE)</f>
         <v>DAMARIS BIVIANA MURCIA SABOYA (103)</v>
       </c>
       <c r="G23" s="39" t="str">
@@ -13493,7 +13493,7 @@
         <v>Nicolas Sarmiento (218)</v>
       </c>
       <c r="F24" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B24,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B24,informacion_extra!A:F,3,FALSE)</f>
         <v>DAMARIS BIVIANA MURCIA SABOYA (103)</v>
       </c>
       <c r="G24" s="39" t="str">
@@ -13536,7 +13536,7 @@
         <v>Nicolas Sarmiento (218)</v>
       </c>
       <c r="F25" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B25,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B25,informacion_extra!A:F,3,FALSE)</f>
         <v>DAMARIS BIVIANA MURCIA SABOYA (103)</v>
       </c>
       <c r="G25" s="39" t="str">
@@ -13582,7 +13582,7 @@
         <v>Nicolas Sarmiento (218)</v>
       </c>
       <c r="F26" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B26,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B26,informacion_extra!A:F,3,FALSE)</f>
         <v>DAMARIS BIVIANA MURCIA SABOYA (103)</v>
       </c>
       <c r="G26" s="39" t="str">
@@ -13625,7 +13625,7 @@
         <v>Nicolas Sarmiento (218)</v>
       </c>
       <c r="F27" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B27,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B27,informacion_extra!A:F,3,FALSE)</f>
         <v>DAMARIS BIVIANA MURCIA SABOYA (103)</v>
       </c>
       <c r="G27" s="39" t="str">
@@ -13668,7 +13668,7 @@
         <v>Alberto Rivera Betancourt (822)</v>
       </c>
       <c r="F28" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B28,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B28,informacion_extra!A:F,3,FALSE)</f>
         <v>PAULA ANDREA MERCADO FLOREZ (776)</v>
       </c>
       <c r="G28" s="39" t="str">
@@ -13712,7 +13712,7 @@
         <v>Gustavo Marques Cussioli  (244)</v>
       </c>
       <c r="F29" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B29,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B29,informacion_extra!A:F,3,FALSE)</f>
         <v>DAMARIS BIVIANA MURCIA SABOYA (103)</v>
       </c>
       <c r="G29" s="39" t="str">
@@ -13759,7 +13759,7 @@
         <v>Nicolas Sarmiento (218)</v>
       </c>
       <c r="F30" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B30,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B30,informacion_extra!A:F,3,FALSE)</f>
         <v>DAMARIS BIVIANA MURCIA SABOYA (103)</v>
       </c>
       <c r="G30" s="39" t="str">
@@ -13804,7 +13804,7 @@
         <v>Nicolas Sarmiento (218)</v>
       </c>
       <c r="F31" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B31,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B31,informacion_extra!A:F,3,FALSE)</f>
         <v>DAMARIS BIVIANA MURCIA SABOYA (103)</v>
       </c>
       <c r="G31" s="39" t="str">
@@ -13848,7 +13848,7 @@
         <v>Carlos Martins de Lima (778)</v>
       </c>
       <c r="F32" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B32,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B32,informacion_extra!A:F,3,FALSE)</f>
         <v>DAMARIS BIVIANA MURCIA SABOYA (103)</v>
       </c>
       <c r="G32" s="39" t="str">
@@ -13893,7 +13893,7 @@
         <v>Nicolas Sarmiento (218)</v>
       </c>
       <c r="F33" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B33,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B33,informacion_extra!A:F,3,FALSE)</f>
         <v>DAMARIS BIVIANA MURCIA SABOYA (103)</v>
       </c>
       <c r="G33" s="39" t="str">
@@ -13936,7 +13936,7 @@
         <v>Jenny Carolina Suarez (101)</v>
       </c>
       <c r="F34" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B34,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B34,informacion_extra!A:F,3,FALSE)</f>
         <v>MISAEL ENRIQUE ARAUJO DIAZ (701)</v>
       </c>
       <c r="G34" s="39" t="str">
@@ -13981,7 +13981,7 @@
         <v>Oscar Mauricio Parada (49)</v>
       </c>
       <c r="F35" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B35,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B35,informacion_extra!A:F,3,FALSE)</f>
         <v>LEIDY FABIOLA CARDENAS SUAREZ (188)</v>
       </c>
       <c r="G35" s="39" t="str">
@@ -14027,7 +14027,7 @@
         <v>Raphael Gustavo Gimenes Trivaleti (219)</v>
       </c>
       <c r="F36" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B36,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B36,informacion_extra!A:F,3,FALSE)</f>
         <v>ELIZABETH MARIA HERNANDEZ RUEDA (767)</v>
       </c>
       <c r="G36" s="39" t="str">
@@ -14075,7 +14075,7 @@
         <v>Lina María Rodríguez Bailón (171)</v>
       </c>
       <c r="F37" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B37,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B37,informacion_extra!A:F,3,FALSE)</f>
         <v>MISAEL ENRIQUE ARAUJO DIAZ (701)</v>
       </c>
       <c r="G37" s="39" t="str">
@@ -14123,7 +14123,7 @@
         <v>Ana Maria Brito Llerena (151)</v>
       </c>
       <c r="F38" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B38,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B38,informacion_extra!A:F,3,FALSE)</f>
         <v>LINA MARIA SANCHEZ ESCOBAR (771)</v>
       </c>
       <c r="G38" s="39" t="str">
@@ -14169,7 +14169,7 @@
         <v>Diana Carolina Sanchez Aguirre (165)</v>
       </c>
       <c r="F39" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B39,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B39,informacion_extra!A:F,3,FALSE)</f>
         <v>LEIDY FABIOLA CARDENAS SUAREZ (188)</v>
       </c>
       <c r="G39" s="39" t="str">
@@ -14212,7 +14212,7 @@
         <v>Diana Carolina Sanchez Aguirre (165)</v>
       </c>
       <c r="F40" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B40,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B40,informacion_extra!A:F,3,FALSE)</f>
         <v>LEIDY FABIOLA CARDENAS SUAREZ (188)</v>
       </c>
       <c r="G40" s="39" t="str">
@@ -14255,7 +14255,7 @@
         <v>Nurky Castro (46)</v>
       </c>
       <c r="F41" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B41,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B41,informacion_extra!A:F,3,FALSE)</f>
         <v>ANGELA PATRICIA PERDOMO (175)</v>
       </c>
       <c r="G41" s="39" t="str">
@@ -14296,7 +14296,7 @@
         <v>Nurky Castro (46)</v>
       </c>
       <c r="F42" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B42,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B42,informacion_extra!A:F,3,FALSE)</f>
         <v>ANGELA PATRICIA PERDOMO (175)</v>
       </c>
       <c r="G42" s="39" t="str">
@@ -14339,7 +14339,7 @@
         <v>Juan Pablo Sanchez Martinez (125)</v>
       </c>
       <c r="F43" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B43,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B43,informacion_extra!A:F,3,FALSE)</f>
         <v>LINA MARIA SANCHEZ ESCOBAR (771)</v>
       </c>
       <c r="G43" s="62" t="str">
@@ -14385,7 +14385,7 @@
         <v>Ana Maria Brito Llerena (151)</v>
       </c>
       <c r="F44" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B44,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B44,informacion_extra!A:F,3,FALSE)</f>
         <v>LINA MARIA SANCHEZ ESCOBAR (771)</v>
       </c>
       <c r="G44" s="39" t="str">
@@ -14433,7 +14433,7 @@
         <v>Raphael Gustavo Gimenes Trivaleti (219)</v>
       </c>
       <c r="F45" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B45,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B45,informacion_extra!A:F,3,FALSE)</f>
         <v>LINA MARIA SANCHEZ ESCOBAR (771)</v>
       </c>
       <c r="G45" s="39" t="str">
@@ -14481,7 +14481,7 @@
         <v>Alvaro Arturo Cortes Barreto (92)</v>
       </c>
       <c r="F46" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B46,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B46,informacion_extra!A:F,3,FALSE)</f>
         <v>LINA MARIA SANCHEZ ESCOBAR (771)</v>
       </c>
       <c r="G46" s="39" t="str">
@@ -14527,7 +14527,7 @@
         <v>Ana Maria Brito Llerena (151)</v>
       </c>
       <c r="F47" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B47,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B47,informacion_extra!A:F,3,FALSE)</f>
         <v>LINA MARIA SANCHEZ ESCOBAR (771)</v>
       </c>
       <c r="G47" s="39" t="str">
@@ -14575,7 +14575,7 @@
         <v>Ana Maria Brito Llerena (151)</v>
       </c>
       <c r="F48" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B48,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B48,informacion_extra!A:F,3,FALSE)</f>
         <v>ELIZABETH MARIA HERNANDEZ RUEDA (767)</v>
       </c>
       <c r="G48" s="39" t="str">
@@ -14618,7 +14618,7 @@
         <v>ANDRES FELIPE ESCOBAR CORREA (260)</v>
       </c>
       <c r="F49" s="26" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B49,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B49,informacion_extra!A:F,3,FALSE)</f>
         <v>ANDRES FELIPE ESCOBAR CORREA (260)</v>
       </c>
       <c r="G49" s="30" t="str">
@@ -14662,7 +14662,7 @@
         <v>ANDRES FELIPE ESCOBAR CORREA (260)</v>
       </c>
       <c r="F50" s="49" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B50,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B50,informacion_extra!A:F,3,FALSE)</f>
         <v>ANDRES FELIPE ESCOBAR CORREA (260)</v>
       </c>
       <c r="G50" s="50" t="str">
@@ -14703,7 +14703,7 @@
         <v>Manuel Escalante (131)</v>
       </c>
       <c r="F51" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B51,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B51,informacion_extra!A:F,3,FALSE)</f>
         <v>MANUEL HERNANDO SANTA JARA (132)</v>
       </c>
       <c r="G51" s="39" t="str">
@@ -14744,7 +14744,7 @@
         <v>Lina María Rodríguez Bailón (171)</v>
       </c>
       <c r="F52" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B52,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B52,informacion_extra!A:F,3,FALSE)</f>
         <v>MISAEL ENRIQUE ARAUJO DIAZ (701)</v>
       </c>
       <c r="G52" s="39" t="str">
@@ -14785,7 +14785,7 @@
         <v>Raphael Gustavo Gimenes Trivaleti (219)</v>
       </c>
       <c r="F53" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B53,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B53,informacion_extra!A:F,3,FALSE)</f>
         <v>LINA MARIA SANCHEZ ESCOBAR (771)</v>
       </c>
       <c r="G53" s="39" t="str">
@@ -14826,7 +14826,7 @@
         <v>Oscar Mauricio Parada (49)</v>
       </c>
       <c r="F54" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B54,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B54,informacion_extra!A:F,3,FALSE)</f>
         <v>SEBASTIAN GALLEGO VILLEGAS (147)</v>
       </c>
       <c r="G54" s="39" t="str">
@@ -14865,7 +14865,7 @@
         <v>Oscar Mauricio Parada (49)</v>
       </c>
       <c r="F55" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B55,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B55,informacion_extra!A:F,3,FALSE)</f>
         <v>SEBASTIAN GALLEGO VILLEGAS (147)</v>
       </c>
       <c r="G55" s="39" t="str">
@@ -14904,7 +14904,7 @@
         <v>Oscar Mauricio Parada (49)</v>
       </c>
       <c r="F56" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B56,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B56,informacion_extra!A:F,3,FALSE)</f>
         <v>SEBASTIAN GALLEGO VILLEGAS (147)</v>
       </c>
       <c r="G56" s="39" t="str">
@@ -14943,7 +14943,7 @@
         <v>Manuel Escalante (131)</v>
       </c>
       <c r="F57" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B57,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B57,informacion_extra!A:F,3,FALSE)</f>
         <v>ANGELA PATRICIA PERDOMO (175)</v>
       </c>
       <c r="G57" s="39" t="str">
@@ -14984,7 +14984,7 @@
         <v>Manuel Escalante (131)</v>
       </c>
       <c r="F58" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B58,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B58,informacion_extra!A:F,3,FALSE)</f>
         <v>ANGELA PATRICIA PERDOMO (175)</v>
       </c>
       <c r="G58" s="39" t="str">
@@ -15027,7 +15027,7 @@
         <v>Manuel Escalante (131)</v>
       </c>
       <c r="F59" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B59,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B59,informacion_extra!A:F,3,FALSE)</f>
         <v>ANGELA PATRICIA PERDOMO (175)</v>
       </c>
       <c r="G59" s="39" t="str">
@@ -15068,7 +15068,7 @@
         <v>John Alejandro Rodriguez (41)</v>
       </c>
       <c r="F60" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B60,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B60,informacion_extra!A:F,3,FALSE)</f>
         <v>GLORIA ELENA AGUDELO ARENAS (181)</v>
       </c>
       <c r="G60" s="39" t="str">
@@ -15111,7 +15111,7 @@
         <v>Manuel Escalante (131)</v>
       </c>
       <c r="F61" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B61,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B61,informacion_extra!A:F,3,FALSE)</f>
         <v>ANGELA PATRICIA PERDOMO (175)</v>
       </c>
       <c r="G61" s="39" t="str">
@@ -15154,7 +15154,7 @@
         <v>Alberto Rivera Betancourt (822)</v>
       </c>
       <c r="F62" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B62,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B62,informacion_extra!A:F,3,FALSE)</f>
         <v>SINDY CRISTINA ALZATE ARIAS (201)</v>
       </c>
       <c r="G62" s="39" t="str">
@@ -15193,7 +15193,7 @@
         <v>Juan Manuel Ossa Botero (40)</v>
       </c>
       <c r="F63" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B63,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B63,informacion_extra!A:F,3,FALSE)</f>
         <v>ADRIANA CAROLINA PEREZ ORTIZ (327)</v>
       </c>
       <c r="G63" s="39" t="str">
@@ -15232,7 +15232,7 @@
         <v>Nicolas Sarmiento (218)</v>
       </c>
       <c r="F64" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B64,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B64,informacion_extra!A:F,3,FALSE)</f>
         <v>DAMARIS BIVIANA MURCIA SABOYA (103)</v>
       </c>
       <c r="G64" s="39" t="str">
@@ -15273,7 +15273,7 @@
         <v>Manuel Escalante (131)</v>
       </c>
       <c r="F65" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B65,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B65,informacion_extra!A:F,3,FALSE)</f>
         <v>ANGELA PATRICIA PERDOMO (175)</v>
       </c>
       <c r="G65" s="39" t="str">
@@ -15312,7 +15312,7 @@
         <v>Manuel Escalante (131)</v>
       </c>
       <c r="F66" s="14" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B66,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B66,informacion_extra!A:F,3,FALSE)</f>
         <v>ANGELA PATRICIA PERDOMO (175)</v>
       </c>
       <c r="G66" s="74" t="str">
@@ -15351,7 +15351,7 @@
         <v>Manuel Escalante (131)</v>
       </c>
       <c r="F67" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B67,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B67,informacion_extra!A:F,3,FALSE)</f>
         <v>ANGELA PATRICIA PERDOMO (175)</v>
       </c>
       <c r="G67" s="39" t="str">
@@ -15390,7 +15390,7 @@
         <v>Manuel Escalante (131)</v>
       </c>
       <c r="F68" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B68,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B68,informacion_extra!A:F,3,FALSE)</f>
         <v>ANGELA PATRICIA PERDOMO (175)</v>
       </c>
       <c r="G68" s="39" t="str">
@@ -15429,7 +15429,7 @@
         <v>Ana Maria Brito Llerena (151)</v>
       </c>
       <c r="F69" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B69,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B69,informacion_extra!A:F,3,FALSE)</f>
         <v>LINA MARIA SANCHEZ ESCOBAR (771)</v>
       </c>
       <c r="G69" s="39" t="str">
@@ -15470,7 +15470,7 @@
         <v>Elkin Dario Fernandez Camacho (166)</v>
       </c>
       <c r="F70" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B70,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B70,informacion_extra!A:F,3,FALSE)</f>
         <v>LEIDY FABIOLA CARDENAS SUAREZ (188)</v>
       </c>
       <c r="G70" s="39" t="str">
@@ -15505,7 +15505,7 @@
         <v>LEIDY FABIOLA CARDENAS SUAREZ (188)</v>
       </c>
       <c r="F71" s="6" t="str">
-        <f>+VLOOKUP(seguimiento_defectos!B71,informacion_extra!A:F,3,FALSE)</f>
+        <f>+VLOOKUP(seguimiento_detalles_defecto!B71,informacion_extra!A:F,3,FALSE)</f>
         <v>LEIDY FABIOLA CARDENAS SUAREZ (188)</v>
       </c>
       <c r="G71" s="39" t="str">
